--- a/default_template/template_international.xlsx
+++ b/default_template/template_international.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'List'!$A$1:$I$63</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Report'!$A$1:$Q$27</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -202,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,6 +268,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -653,7 +659,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -672,7 +678,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LEK Partners</t>
+          <t>KIOTI</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1503,9 @@
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="G63:I63"/>
   </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1505,7 +1513,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1532,7 +1540,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>LEK Partners</t>
+          <t>KIOTI</t>
         </is>
       </c>
     </row>
@@ -1580,6 +1588,16 @@
       </c>
       <c r="L7" s="24" t="n"/>
     </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="6" t="inlineStr"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="K8" s="25" t="n"/>
+      <c r="M8" s="25" t="n"/>
+      <c r="O8" s="25" t="n"/>
+    </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
@@ -1621,7 +1639,7 @@
           <t>Sun</t>
         </is>
       </c>
-      <c r="Q9" s="25" t="inlineStr">
+      <c r="Q9" s="26" t="inlineStr">
         <is>
           <t>Weekly
 Total (USD)</t>
@@ -1630,80 +1648,80 @@
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="6" t="inlineStr"/>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Foreign</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>Foreign</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>Foreign</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Foreign</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="J10" s="27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="27" t="inlineStr">
         <is>
           <t>Foreign</t>
         </is>
       </c>
-      <c r="L10" s="26" t="inlineStr">
+      <c r="L10" s="27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t>Foreign</t>
         </is>
       </c>
-      <c r="N10" s="26" t="inlineStr">
+      <c r="N10" s="27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="O10" s="26" t="inlineStr">
+      <c r="O10" s="27" t="inlineStr">
         <is>
           <t>Foreign</t>
         </is>
       </c>
-      <c r="P10" s="26" t="inlineStr">
+      <c r="P10" s="27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr"/>
+      <c r="Q10" s="26" t="inlineStr"/>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Breakfast</t>
         </is>
@@ -1722,13 +1740,13 @@
       <c r="N11" s="16" t="n"/>
       <c r="O11" s="16" t="n"/>
       <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="28">
+      <c r="Q11" s="29">
         <f>D11+F11+H11+J11+L11+N11+P11</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
@@ -1747,13 +1765,13 @@
       <c r="N12" s="11" t="n"/>
       <c r="O12" s="11" t="n"/>
       <c r="P12" s="11" t="n"/>
-      <c r="Q12" s="28">
+      <c r="Q12" s="29">
         <f>D12+F12+H12+J12+L12+N12+P12</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
@@ -1772,13 +1790,13 @@
       <c r="N13" s="16" t="n"/>
       <c r="O13" s="16" t="n"/>
       <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="28">
+      <c r="Q13" s="29">
         <f>D13+F13+H13+J13+L13+N13+P13</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
@@ -1797,13 +1815,13 @@
       <c r="N14" s="11" t="n"/>
       <c r="O14" s="11" t="n"/>
       <c r="P14" s="11" t="n"/>
-      <c r="Q14" s="28">
+      <c r="Q14" s="29">
         <f>D14+F14+H14+J14+L14+N14+P14</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Lodging / Hotel</t>
         </is>
@@ -1822,13 +1840,13 @@
       <c r="N15" s="16" t="n"/>
       <c r="O15" s="16" t="n"/>
       <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="28">
+      <c r="Q15" s="29">
         <f>D15+F15+H15+J15+L15+N15+P15</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Airfare</t>
         </is>
@@ -1847,13 +1865,13 @@
       <c r="N16" s="11" t="n"/>
       <c r="O16" s="11" t="n"/>
       <c r="P16" s="11" t="n"/>
-      <c r="Q16" s="28">
+      <c r="Q16" s="29">
         <f>D16+F16+H16+J16+L16+N16+P16</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Car Rental</t>
         </is>
@@ -1872,13 +1890,13 @@
       <c r="N17" s="16" t="n"/>
       <c r="O17" s="16" t="n"/>
       <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="28">
+      <c r="Q17" s="29">
         <f>D17+F17+H17+J17+L17+N17+P17</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Taxi / Rideshare</t>
         </is>
@@ -1897,13 +1915,13 @@
       <c r="N18" s="11" t="n"/>
       <c r="O18" s="11" t="n"/>
       <c r="P18" s="11" t="n"/>
-      <c r="Q18" s="28">
+      <c r="Q18" s="29">
         <f>D18+F18+H18+J18+L18+N18+P18</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Mileage</t>
         </is>
@@ -1922,13 +1940,13 @@
       <c r="N19" s="16" t="n"/>
       <c r="O19" s="16" t="n"/>
       <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="28">
+      <c r="Q19" s="29">
         <f>D19+F19+H19+J19+L19+N19+P19</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Parking / Tolls</t>
         </is>
@@ -1947,13 +1965,13 @@
       <c r="N20" s="11" t="n"/>
       <c r="O20" s="11" t="n"/>
       <c r="P20" s="11" t="n"/>
-      <c r="Q20" s="28">
+      <c r="Q20" s="29">
         <f>D20+F20+H20+J20+L20+N20+P20</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>Phone / Internet</t>
         </is>
@@ -1972,13 +1990,13 @@
       <c r="N21" s="16" t="n"/>
       <c r="O21" s="16" t="n"/>
       <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="28">
+      <c r="Q21" s="29">
         <f>D21+F21+H21+J21+L21+N21+P21</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>Miscellaneous</t>
         </is>
@@ -1997,53 +2015,53 @@
       <c r="N22" s="11" t="n"/>
       <c r="O22" s="11" t="n"/>
       <c r="P22" s="11" t="n"/>
-      <c r="Q22" s="28">
+      <c r="Q22" s="29">
         <f>D22+F22+H22+J22+L22+N22+P22</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>DAILY TOTAL (USD)</t>
         </is>
       </c>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="31">
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="32">
         <f>SUM(D11:D22)</f>
         <v/>
       </c>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="31">
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="32">
         <f>SUM(F11:F22)</f>
         <v/>
       </c>
-      <c r="G23" s="30" t="n"/>
-      <c r="H23" s="31">
+      <c r="G23" s="31" t="n"/>
+      <c r="H23" s="32">
         <f>SUM(H11:H22)</f>
         <v/>
       </c>
-      <c r="I23" s="30" t="n"/>
-      <c r="J23" s="31">
+      <c r="I23" s="31" t="n"/>
+      <c r="J23" s="32">
         <f>SUM(J11:J22)</f>
         <v/>
       </c>
-      <c r="K23" s="30" t="n"/>
-      <c r="L23" s="31">
+      <c r="K23" s="31" t="n"/>
+      <c r="L23" s="32">
         <f>SUM(L11:L22)</f>
         <v/>
       </c>
-      <c r="M23" s="30" t="n"/>
-      <c r="N23" s="31">
+      <c r="M23" s="31" t="n"/>
+      <c r="N23" s="32">
         <f>SUM(N11:N22)</f>
         <v/>
       </c>
-      <c r="O23" s="30" t="n"/>
-      <c r="P23" s="31">
+      <c r="O23" s="31" t="n"/>
+      <c r="P23" s="32">
         <f>SUM(P11:P22)</f>
         <v/>
       </c>
-      <c r="Q23" s="32">
+      <c r="Q23" s="33">
         <f>D23+F23+H23+J23+L23+N23+P23</f>
         <v/>
       </c>
@@ -2088,7 +2106,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="51">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="K25:O25"/>
     <mergeCell ref="L7:P7"/>
@@ -2097,9 +2115,12 @@
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="O9:P9"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="D5:G5"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="K26:O26"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="G9:H9"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="I4:K4"/>
@@ -2114,25 +2135,32 @@
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="K8:L8"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A7:C7"/>
     <mergeCell ref="K27:O27"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="O8:P8"/>
     <mergeCell ref="F27:J27"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>